--- a/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-16_Melhoria_Kaizen_EMAS.xlsx
+++ b/SGI_Sistema-de-gestao-integrado/SGA_Sistema-de-gestao-ambiental/Registos_SGA_Plasticom/SGA-16_Melhoria_Kaizen_EMAS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project Portfolios\manufacturing-performance-analytics\SGI_Sistema-de-gestao-integrado\SGA_Sistema-de-gestao-ambiental\Registos_SGA_Plasticom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1044E5F9-F098-4AB0-8A47-F001E72C94B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DD0FE38-4B8F-4008-A8B0-E8293957F1D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1920" yWindow="1920" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1094,7 +1094,7 @@
     <t>MWh</t>
   </si>
   <si>
-    <t>É o 1.º custo ambiental e a origem de ≈ 99% das emissões de GEE: injeção e sopro são eletrointensivos (≈ 7,2 GWh/ano, instalação SGCIE).</t>
+    <t>É o 1.º custo ambiental e a origem de ≈ 99% das emissões de GEE: injeção e sopro são eletrointensivos (≈ 7,8 GWh/ano, instalação SGCIE).</t>
   </si>
   <si>
     <t>EMAS-01b</t>
